--- a/IT23324992_Test cases.xlsx
+++ b/IT23324992_Test cases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\IT23324992\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\ITPM_Assignment1_IT23324992\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="285">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -156,9 +156,6 @@
   </si>
   <si>
     <t>Requests</t>
-  </si>
-  <si>
-    <t>Rationale: The input contains common Singlish transliteration patterns that the system might fail to process correctly.</t>
   </si>
   <si>
     <t>Neg_0008</t>
@@ -976,9 +973,6 @@
 Evidence: "mokak?? mata oya kiyana de nm therenne na…" Rationale: It uses punctuation marks  .  and !</t>
   </si>
   <si>
-    <t>Rationale: Informal conversational responses using abbreviations like “mn”, “na na”. System fails to interpret shortened Singlish forms.</t>
-  </si>
-  <si>
     <t>Rationale: Informal conversational responses using abbreviations like “mata”, “ow ow”. System fails to interpret shortened Singlish forms.</t>
   </si>
   <si>
@@ -1065,6 +1059,16 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>Rationale: The input contains repeated words (“හිමිං හිමිං”), which are used to emphasize meaning (slowly/gradually). The system fails to correctly preserve or normalize repeated word structures during conversion.</t>
+  </si>
+  <si>
+    <t>Rationale: The input includes repetition (“හෙට හෙට”) to express continuous postponement. Handling such repeated expressions is important for maintaining semantic meaning, but the system distorts these repetitions in the output.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rationale:Input includes informal repetition (“නෑ නෑ”) and mixed English terms like “notice”, “deadline”. The system fails to preserve these, causing distorted output.
+</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1472,7 @@
     <col min="3" max="4" width="47.88671875" style="6" customWidth="1"/>
     <col min="5" max="5" width="50.21875" style="6" customWidth="1"/>
     <col min="6" max="6" width="22.5546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="41.6640625" style="6" customWidth="1"/>
     <col min="8" max="8" width="79.77734375" style="6" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" style="6" customWidth="1"/>
     <col min="10" max="10" width="16" style="6" customWidth="1"/>
@@ -1576,7 +1580,7 @@
         <v>25</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1602,7 +1606,7 @@
         <v>25</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1628,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1654,7 +1658,7 @@
         <v>34</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1680,24 +1684,24 @@
         <v>44</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>13</v>
@@ -1706,1099 +1710,1099 @@
         <v>44</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="H10" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="F11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>45</v>
+      <c r="H12" s="3" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="D13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="F17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="F19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="H22" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="F23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="H24" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="F25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="H26" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="F27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="H28" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="F29" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="H30" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="F31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="H32" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="F33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="H34" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="F35" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="F37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="H38" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="F39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="H40" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="H42" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="H44" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="F46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="H46" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="E48" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="F48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="H48" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="F49" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="F50" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="F51" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
